--- a/diseases/d092/2005-2009.xlsx
+++ b/diseases/d092/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>219</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>4.174543973959995</v>
       </c>
@@ -1787,9 +1784,6 @@
       <c r="O7" t="n">
         <v>69</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>1.492497281059301</v>
       </c>
@@ -2331,9 +2325,6 @@
       <c r="O10" t="n">
         <v>191</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>3.640812324321274</v>
       </c>
@@ -2966,9 +2957,6 @@
       <c r="O13" t="n">
         <v>63</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>1.362714908793275</v>
       </c>
@@ -3510,9 +3498,6 @@
       <c r="O16" t="n">
         <v>187</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>3.564564945801457</v>
       </c>
@@ -4145,9 +4130,6 @@
       <c r="O19" t="n">
         <v>87</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>1.88184439785738</v>
       </c>
@@ -4689,9 +4671,6 @@
       <c r="O22" t="n">
         <v>201</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>3.831430770620817</v>
       </c>
@@ -5324,9 +5303,6 @@
       <c r="O25" t="n">
         <v>98</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>2.119778747011761</v>
       </c>
@@ -5868,9 +5844,6 @@
       <c r="O28" t="n">
         <v>205</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>3.907678149140635</v>
       </c>
@@ -6503,9 +6476,6 @@
       <c r="O31" t="n">
         <v>129</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>2.790321003719563</v>
       </c>
@@ -7047,9 +7017,6 @@
       <c r="O34" t="n">
         <v>316</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>6.023542903065565</v>
       </c>
@@ -7682,9 +7649,6 @@
       <c r="O37" t="n">
         <v>372</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>8.046507080493623</v>
       </c>
@@ -8226,9 +8190,6 @@
       <c r="O40" t="n">
         <v>864</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>16.46943376028053</v>
       </c>
@@ -8861,9 +8822,6 @@
       <c r="O43" t="n">
         <v>585</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>12.65378129593755</v>
       </c>
@@ -9405,9 +9363,6 @@
       <c r="O46" t="n">
         <v>615</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>11.7230344474219</v>
       </c>
@@ -10040,9 +9995,6 @@
       <c r="O49" t="n">
         <v>542</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>11.7236742946977</v>
       </c>
@@ -10584,9 +10536,6 @@
       <c r="O52" t="n">
         <v>441</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>8.406273481809853</v>
       </c>
@@ -11219,9 +11168,6 @@
       <c r="O55" t="n">
         <v>256</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>5.537381216683784</v>
       </c>
@@ -11763,9 +11709,6 @@
       <c r="O58" t="n">
         <v>313</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>5.966357369175701</v>
       </c>
@@ -12398,9 +12341,6 @@
       <c r="O61" t="n">
         <v>165</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>3.56901523731572</v>
       </c>
@@ -12942,9 +12882,6 @@
       <c r="O64" t="n">
         <v>236</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>4.498595332669219</v>
       </c>
@@ -13577,9 +13514,6 @@
       <c r="O67" t="n">
         <v>134</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>2.898472980607918</v>
       </c>
@@ -14121,9 +14055,6 @@
       <c r="O70" t="n">
         <v>215</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>4.098296595440178</v>
       </c>
@@ -14756,9 +14687,6 @@
       <c r="O73" t="n">
         <v>132</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>2.855212189852576</v>
       </c>
@@ -15300,9 +15228,6 @@
       <c r="O76" t="n">
         <v>227</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>4.310470465064633</v>
       </c>
@@ -16174,9 +16099,6 @@
       <c r="O80" t="n">
         <v>100</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>2.145695284662956</v>
       </c>
@@ -16718,9 +16640,6 @@
       <c r="O83" t="n">
         <v>199</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>3.778782478184415</v>
       </c>
@@ -17353,9 +17272,6 @@
       <c r="O86" t="n">
         <v>72</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>1.544900604957328</v>
       </c>
@@ -17897,9 +17813,6 @@
       <c r="O89" t="n">
         <v>192</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>3.64586048146436</v>
       </c>
@@ -18532,9 +18445,6 @@
       <c r="O92" t="n">
         <v>80</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>1.716556227730365</v>
       </c>
@@ -19076,9 +18986,6 @@
       <c r="O95" t="n">
         <v>184</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>3.493949628070011</v>
       </c>
@@ -19711,9 +19618,6 @@
       <c r="O98" t="n">
         <v>111</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>2.381721765975882</v>
       </c>
@@ -20255,9 +20159,6 @@
       <c r="O101" t="n">
         <v>217</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>4.120581898321698</v>
       </c>
@@ -20890,9 +20791,6 @@
       <c r="O104" t="n">
         <v>190</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>4.076821040859617</v>
       </c>
@@ -21434,9 +21332,6 @@
       <c r="O107" t="n">
         <v>362</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>6.873966116094262</v>
       </c>
@@ -22069,9 +21964,6 @@
       <c r="O110" t="n">
         <v>344</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>7.38119177924057</v>
       </c>
@@ -22613,9 +22505,6 @@
       <c r="O113" t="n">
         <v>561</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>10.65274859427868</v>
       </c>
@@ -23248,9 +23137,6 @@
       <c r="O116" t="n">
         <v>495</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>10.62119165908163</v>
       </c>
@@ -23792,9 +23678,6 @@
       <c r="O119" t="n">
         <v>471</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>8.943751493592258</v>
       </c>
@@ -24427,9 +24310,6 @@
       <c r="O122" t="n">
         <v>440</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>9.441059252517007</v>
       </c>
@@ -24971,9 +24851,6 @@
       <c r="O125" t="n">
         <v>267</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>5.070024732036376</v>
       </c>
@@ -25606,9 +25483,6 @@
       <c r="O128" t="n">
         <v>187</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>4.012450182319728</v>
       </c>
@@ -26150,9 +26024,6 @@
       <c r="O131" t="n">
         <v>306</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>5.810590142333823</v>
       </c>
@@ -26785,9 +26656,6 @@
       <c r="O134" t="n">
         <v>283</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>6.072317655596167</v>
       </c>
@@ -27329,9 +27197,6 @@
       <c r="O137" t="n">
         <v>227</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>4.310470465064633</v>
       </c>
@@ -27964,9 +27829,6 @@
       <c r="O140" t="n">
         <v>179</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>3.840794559546692</v>
       </c>
@@ -28508,9 +28370,6 @@
       <c r="O143" t="n">
         <v>230</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>4.367437035087515</v>
       </c>
@@ -29143,9 +29002,6 @@
       <c r="O146" t="n">
         <v>107</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>2.295893954589364</v>
       </c>
@@ -29687,9 +29543,6 @@
       <c r="O149" t="n">
         <v>301</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>5.691368972774079</v>
       </c>
@@ -30561,9 +30414,6 @@
       <c r="O153" t="n">
         <v>109</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>2.314711584812944</v>
       </c>
@@ -31105,9 +30955,6 @@
       <c r="O156" t="n">
         <v>244</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>4.613601426434801</v>
       </c>
@@ -31740,9 +31587,6 @@
       <c r="O159" t="n">
         <v>80</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>1.698870887936105</v>
       </c>
@@ -32284,9 +32128,6 @@
       <c r="O162" t="n">
         <v>226</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>4.273253780222398</v>
       </c>
@@ -32919,9 +32760,6 @@
       <c r="O165" t="n">
         <v>117</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>2.484598673606554</v>
       </c>
@@ -33463,9 +33301,6 @@
       <c r="O168" t="n">
         <v>175</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>3.308935449287255</v>
       </c>
@@ -34098,9 +33933,6 @@
       <c r="O171" t="n">
         <v>137</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>2.909316395590581</v>
       </c>
@@ -34642,9 +34474,6 @@
       <c r="O174" t="n">
         <v>234</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>4.424519400761244</v>
       </c>
@@ -35277,9 +35106,6 @@
       <c r="O177" t="n">
         <v>236</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>5.011669119411511</v>
       </c>
@@ -35821,9 +35647,6 @@
       <c r="O180" t="n">
         <v>324</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>6.126257631823261</v>
       </c>
@@ -36456,9 +36279,6 @@
       <c r="O183" t="n">
         <v>315</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>6.689304121248415</v>
       </c>
@@ -37000,9 +36820,6 @@
       <c r="O186" t="n">
         <v>628</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>11.87435121229941</v>
       </c>
@@ -37635,9 +37452,6 @@
       <c r="O189" t="n">
         <v>609</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>12.9326546344136</v>
       </c>
@@ -38179,9 +37993,6 @@
       <c r="O192" t="n">
         <v>505</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>9.54864229651465</v>
       </c>
@@ -38814,9 +38625,6 @@
       <c r="O195" t="n">
         <v>444</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>9.428733428045385</v>
       </c>
@@ -39358,9 +39166,6 @@
       <c r="O198" t="n">
         <v>355</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>6.712411911411289</v>
       </c>
@@ -39993,9 +39798,6 @@
       <c r="O201" t="n">
         <v>261</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>5.542566271891544</v>
       </c>
@@ -40537,9 +40339,6 @@
       <c r="O204" t="n">
         <v>373</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>7.052759557623693</v>
       </c>
@@ -41172,9 +40971,6 @@
       <c r="O207" t="n">
         <v>221</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>4.693130827923492</v>
       </c>
@@ -41716,9 +41512,6 @@
       <c r="O210" t="n">
         <v>257</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>4.859408059810426</v>
       </c>
@@ -42351,9 +42144,6 @@
       <c r="O213" t="n">
         <v>181</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>3.843695383955439</v>
       </c>
@@ -42895,9 +42685,6 @@
       <c r="O216" t="n">
         <v>480</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>9.075937232330757</v>
       </c>
@@ -43530,9 +43317,6 @@
       <c r="O219" t="n">
         <v>125</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>2.654485762400165</v>
       </c>
@@ -44074,9 +43858,6 @@
       <c r="O222" t="n">
         <v>395</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>7.43406688439386</v>
       </c>
@@ -44948,9 +44729,6 @@
       <c r="O226" t="n">
         <v>109</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>2.28602540088811</v>
       </c>
@@ -45492,9 +45270,6 @@
       <c r="O229" t="n">
         <v>283</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>5.326179565274589</v>
       </c>
@@ -46127,9 +45902,6 @@
       <c r="O232" t="n">
         <v>96</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>2.013380169589528</v>
       </c>
@@ -46671,9 +46443,6 @@
       <c r="O235" t="n">
         <v>340</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>6.398943647326362</v>
       </c>
@@ -47306,9 +47075,6 @@
       <c r="O238" t="n">
         <v>130</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>2.72645231298582</v>
       </c>
@@ -47850,9 +47616,6 @@
       <c r="O241" t="n">
         <v>249</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>4.686285200541953</v>
       </c>
@@ -48485,9 +48248,6 @@
       <c r="O244" t="n">
         <v>145</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>3.041042964484184</v>
       </c>
@@ -49029,9 +48789,6 @@
       <c r="O247" t="n">
         <v>200</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>3.764084498427271</v>
       </c>
@@ -49664,9 +49421,6 @@
       <c r="O250" t="n">
         <v>194</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>4.068705759378838</v>
       </c>
@@ -50208,9 +49962,6 @@
       <c r="O253" t="n">
         <v>366</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>6.888274632121907</v>
       </c>
@@ -50843,9 +50594,6 @@
       <c r="O256" t="n">
         <v>305</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>6.396676580466731</v>
       </c>
@@ -51387,9 +51135,6 @@
       <c r="O259" t="n">
         <v>681</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>12.81670771714486</v>
       </c>
@@ -52022,9 +51767,6 @@
       <c r="O262" t="n">
         <v>527</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>11.05261822264251</v>
       </c>
@@ -52566,9 +52308,6 @@
       <c r="O265" t="n">
         <v>584</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>10.99112673540763</v>
       </c>
@@ -53201,9 +52940,6 @@
       <c r="O268" t="n">
         <v>513</v>
       </c>
-      <c r="Q268" t="n">
-        <v>0</v>
-      </c>
       <c r="R268" t="n">
         <v>10.75900028124404</v>
       </c>
@@ -53745,9 +53481,6 @@
       <c r="O271" t="n">
         <v>428</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>8.055140826634361</v>
       </c>
@@ -54380,9 +54113,6 @@
       <c r="O274" t="n">
         <v>260</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>5.452904625971639</v>
       </c>
@@ -54924,9 +54654,6 @@
       <c r="O277" t="n">
         <v>389</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>7.321144349441043</v>
       </c>
@@ -55559,9 +55286,6 @@
       <c r="O280" t="n">
         <v>365</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>7.655039186460186</v>
       </c>
@@ -56103,9 +55827,6 @@
       <c r="O283" t="n">
         <v>254</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>4.780387313002635</v>
       </c>
@@ -56738,9 +56459,6 @@
       <c r="O286" t="n">
         <v>142</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>2.978124834184511</v>
       </c>
@@ -57282,9 +57000,6 @@
       <c r="O289" t="n">
         <v>276</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>5.194436607829635</v>
       </c>
@@ -57917,9 +57632,6 @@
       <c r="O292" t="n">
         <v>89</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>1.866571198890292</v>
       </c>
@@ -58461,9 +58173,6 @@
       <c r="O295" t="n">
         <v>355</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>6.649363960241299</v>
       </c>
@@ -59335,9 +59044,6 @@
       <c r="O299" t="n">
         <v>92</v>
       </c>
-      <c r="Q299" t="n">
-        <v>0</v>
-      </c>
       <c r="R299" t="n">
         <v>1.905305291519476</v>
       </c>
@@ -59879,9 +59585,6 @@
       <c r="O302" t="n">
         <v>289</v>
       </c>
-      <c r="Q302" t="n">
-        <v>0</v>
-      </c>
       <c r="R302" t="n">
         <v>5.413144181717565</v>
       </c>
@@ -60514,9 +60217,6 @@
       <c r="O305" t="n">
         <v>81</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>1.677497050142147</v>
       </c>
@@ -61058,9 +60758,6 @@
       <c r="O308" t="n">
         <v>305</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>5.712833824996046</v>
       </c>
@@ -61693,9 +61390,6 @@
       <c r="O311" t="n">
         <v>173</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>3.582802341661623</v>
       </c>
@@ -62237,9 +61931,6 @@
       <c r="O314" t="n">
         <v>275</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>5.150915743848893</v>
       </c>
@@ -62872,9 +62563,6 @@
       <c r="O317" t="n">
         <v>150</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>3.106476018781754</v>
       </c>
@@ -63416,9 +63104,6 @@
       <c r="O320" t="n">
         <v>239</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>4.476614046472311</v>
       </c>
@@ -64051,9 +63736,6 @@
       <c r="O323" t="n">
         <v>215</v>
       </c>
-      <c r="Q323" t="n">
-        <v>0</v>
-      </c>
       <c r="R323" t="n">
         <v>4.452615626920514</v>
       </c>
@@ -64595,9 +64277,6 @@
       <c r="O326" t="n">
         <v>364</v>
       </c>
-      <c r="Q326" t="n">
-        <v>0</v>
-      </c>
       <c r="R326" t="n">
         <v>6.817939384585444</v>
       </c>
@@ -65230,9 +64909,6 @@
       <c r="O329" t="n">
         <v>382</v>
       </c>
-      <c r="Q329" t="n">
-        <v>0</v>
-      </c>
       <c r="R329" t="n">
         <v>7.911158927830867</v>
       </c>
@@ -65774,9 +65450,6 @@
       <c r="O332" t="n">
         <v>796</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>14.90955975310443</v>
       </c>
@@ -66409,9 +66082,6 @@
       <c r="O335" t="n">
         <v>568</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>11.76318919112024</v>
       </c>
@@ -66953,9 +66623,6 @@
       <c r="O338" t="n">
         <v>459</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>8.597346641551425</v>
       </c>
@@ -67588,9 +67255,6 @@
       <c r="O341" t="n">
         <v>398</v>
       </c>
-      <c r="Q341" t="n">
-        <v>0</v>
-      </c>
       <c r="R341" t="n">
         <v>8.242516369834254</v>
       </c>
@@ -68132,9 +67796,6 @@
       <c r="O344" t="n">
         <v>277</v>
       </c>
-      <c r="Q344" t="n">
-        <v>0</v>
-      </c>
       <c r="R344" t="n">
         <v>5.188376949258704</v>
       </c>
@@ -68767,9 +68428,6 @@
       <c r="O347" t="n">
         <v>309</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>6.399340598690414</v>
       </c>
@@ -69311,9 +68969,6 @@
       <c r="O350" t="n">
         <v>286</v>
       </c>
-      <c r="Q350" t="n">
-        <v>0</v>
-      </c>
       <c r="R350" t="n">
         <v>5.356952373602849</v>
       </c>
@@ -69946,9 +69601,6 @@
       <c r="O353" t="n">
         <v>264</v>
       </c>
-      <c r="Q353" t="n">
-        <v>0</v>
-      </c>
       <c r="R353" t="n">
         <v>5.467397793055887</v>
       </c>
@@ -70490,9 +70142,6 @@
       <c r="O356" t="n">
         <v>182</v>
       </c>
-      <c r="Q356" t="n">
-        <v>0</v>
-      </c>
       <c r="R356" t="n">
         <v>3.408969692292722</v>
       </c>
@@ -71125,9 +70774,6 @@
       <c r="O359" t="n">
         <v>117</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>2.423051294649768</v>
       </c>
@@ -71669,9 +71315,6 @@
       <c r="O362" t="n">
         <v>219</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>4.10200199237421</v>
       </c>
@@ -72303,9 +71946,6 @@
       </c>
       <c r="O365" t="n">
         <v>99</v>
-      </c>
-      <c r="Q365" t="n">
-        <v>0</v>
       </c>
       <c r="R365" t="n">
         <v>2.050274172395957</v>
